--- a/backend/Blockchain/leader/excel2.xlsx
+++ b/backend/Blockchain/leader/excel2.xlsx
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -417,46 +429,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Threat ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Source IP</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Target IP</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Start Time</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Attack Count</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
@@ -486,7 +498,7 @@
           <t>10.148.64.251</t>
         </is>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="F2" s="2" t="n">
         <v>46141.43313657407</v>
       </c>
       <c r="G2" t="n">
@@ -522,7 +534,7 @@
           <t>10.148.64.251</t>
         </is>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="F3" s="2" t="n">
         <v>46141.43570601852</v>
       </c>
       <c r="G3" t="n">
@@ -558,7 +570,7 @@
           <t>10.148.64.251</t>
         </is>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="F4" s="2" t="n">
         <v>46141.43732638889</v>
       </c>
       <c r="G4" t="n">
@@ -594,7 +606,7 @@
           <t>192.168.47.159</t>
         </is>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="F5" s="2" t="n">
         <v>46141.4647337963</v>
       </c>
       <c r="G5" t="n">
@@ -630,7 +642,7 @@
           <t>192.168.47.159</t>
         </is>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="F6" s="2" t="n">
         <v>46141.50162037037</v>
       </c>
       <c r="G6" t="n">
@@ -666,7 +678,7 @@
           <t>192.168.47.159</t>
         </is>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="F7" s="2" t="n">
         <v>46141.5015162037</v>
       </c>
       <c r="G7" t="n">
@@ -702,7 +714,7 @@
           <t>192.168.47.159</t>
         </is>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="F8" s="2" t="n">
         <v>46141.50166666666</v>
       </c>
       <c r="G8" t="n">
@@ -738,7 +750,7 @@
           <t>192.168.47.159</t>
         </is>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="F9" s="2" t="n">
         <v>46141.50203703704</v>
       </c>
       <c r="G9" t="n">
@@ -774,7 +786,7 @@
           <t>192.168.85.159</t>
         </is>
       </c>
-      <c r="F10" s="1" t="n">
+      <c r="F10" s="2" t="n">
         <v>46141.64646990741</v>
       </c>
       <c r="G10" t="n">
@@ -810,7 +822,7 @@
           <t>192.168.85.159</t>
         </is>
       </c>
-      <c r="F11" s="1" t="n">
+      <c r="F11" s="2" t="n">
         <v>46141.64646990741</v>
       </c>
       <c r="G11" t="n">
@@ -846,7 +858,7 @@
           <t>192.168.85.159</t>
         </is>
       </c>
-      <c r="F12" s="1" t="n">
+      <c r="F12" s="2" t="n">
         <v>46141.66327546296</v>
       </c>
       <c r="G12" t="n">
@@ -882,7 +894,7 @@
           <t>192.168.85.159</t>
         </is>
       </c>
-      <c r="F13" s="1" t="n">
+      <c r="F13" s="2" t="n">
         <v>46141.66327546296</v>
       </c>
       <c r="G13" t="n">
@@ -918,7 +930,7 @@
           <t>192.168.85.159</t>
         </is>
       </c>
-      <c r="F14" s="1" t="n">
+      <c r="F14" s="2" t="n">
         <v>46141.66371527778</v>
       </c>
       <c r="G14" t="n">
@@ -954,7 +966,7 @@
           <t>192.168.85.159</t>
         </is>
       </c>
-      <c r="F15" s="1" t="n">
+      <c r="F15" s="2" t="n">
         <v>46141.67614583333</v>
       </c>
       <c r="G15" t="n">
@@ -990,7 +1002,7 @@
           <t>192.168.85.159</t>
         </is>
       </c>
-      <c r="F16" s="1" t="n">
+      <c r="F16" s="2" t="n">
         <v>46141.67618055556</v>
       </c>
       <c r="G16" t="n">
@@ -1026,7 +1038,7 @@
           <t>192.168.85.159</t>
         </is>
       </c>
-      <c r="F17" s="1" t="n">
+      <c r="F17" s="2" t="n">
         <v>46142.92621527778</v>
       </c>
       <c r="G17" t="n">
@@ -1062,7 +1074,7 @@
           <t>192.168.185.159</t>
         </is>
       </c>
-      <c r="F18" s="1" t="n">
+      <c r="F18" s="2" t="n">
         <v>46141.90363425926</v>
       </c>
       <c r="G18" t="n">
@@ -1098,7 +1110,7 @@
           <t>192.168.185.159</t>
         </is>
       </c>
-      <c r="F19" s="1" t="n">
+      <c r="F19" s="2" t="n">
         <v>46141.90368055556</v>
       </c>
       <c r="G19" t="n">
@@ -1134,7 +1146,7 @@
           <t>192.168.29.124</t>
         </is>
       </c>
-      <c r="F20" s="1" t="n">
+      <c r="F20" s="2" t="n">
         <v>46141.91077546297</v>
       </c>
       <c r="G20" t="n">
@@ -1170,7 +1182,7 @@
           <t>10.148.64.251</t>
         </is>
       </c>
-      <c r="F21" s="1" t="n">
+      <c r="F21" s="2" t="n">
         <v>46141.91701388889</v>
       </c>
       <c r="G21" t="n">
@@ -1206,7 +1218,7 @@
           <t>10.148.64.251</t>
         </is>
       </c>
-      <c r="F22" s="1" t="n">
+      <c r="F22" s="2" t="n">
         <v>46141.91935185185</v>
       </c>
       <c r="G22" t="n">
@@ -1242,7 +1254,7 @@
           <t>192.168.29.124</t>
         </is>
       </c>
-      <c r="F23" s="1" t="n">
+      <c r="F23" s="2" t="n">
         <v>46141.91995370371</v>
       </c>
       <c r="G23" t="n">
@@ -1278,7 +1290,7 @@
           <t>10.148.64.251</t>
         </is>
       </c>
-      <c r="F24" s="1" t="n">
+      <c r="F24" s="2" t="n">
         <v>46141.92134259259</v>
       </c>
       <c r="G24" t="n">
@@ -1314,7 +1326,7 @@
           <t>10.148.64.251</t>
         </is>
       </c>
-      <c r="F25" s="1" t="n">
+      <c r="F25" s="2" t="n">
         <v>46141.92164351852</v>
       </c>
       <c r="G25" t="n">
@@ -1350,7 +1362,7 @@
           <t>192.168.150.159</t>
         </is>
       </c>
-      <c r="F26" s="1" t="n">
+      <c r="F26" s="2" t="n">
         <v>46142.41667824074</v>
       </c>
       <c r="G26" t="n">
@@ -1386,7 +1398,7 @@
           <t>192.168.150.159</t>
         </is>
       </c>
-      <c r="F27" s="1" t="n">
+      <c r="F27" s="2" t="n">
         <v>46142.43975694444</v>
       </c>
       <c r="G27" t="n">
@@ -1422,7 +1434,7 @@
           <t>192.168.150.159</t>
         </is>
       </c>
-      <c r="F28" s="1" t="n">
+      <c r="F28" s="2" t="n">
         <v>46142.46760416667</v>
       </c>
       <c r="G28" t="n">
@@ -1458,7 +1470,7 @@
           <t>192.168.150.159</t>
         </is>
       </c>
-      <c r="F29" s="1" t="n">
+      <c r="F29" s="2" t="n">
         <v>46142.49922453704</v>
       </c>
       <c r="G29" t="n">
@@ -1494,7 +1506,7 @@
           <t>192.168.150.159</t>
         </is>
       </c>
-      <c r="F30" s="1" t="n">
+      <c r="F30" s="2" t="n">
         <v>46142.50458333334</v>
       </c>
       <c r="G30" t="n">
@@ -1530,7 +1542,7 @@
           <t>10.0.2.15</t>
         </is>
       </c>
-      <c r="F31" s="1" t="n">
+      <c r="F31" s="2" t="n">
         <v>46142.55274305555</v>
       </c>
       <c r="G31" t="n">
@@ -1566,7 +1578,7 @@
           <t>10.0.2.15</t>
         </is>
       </c>
-      <c r="F32" s="1" t="n">
+      <c r="F32" s="2" t="n">
         <v>46142.55290509259</v>
       </c>
       <c r="G32" t="n">
@@ -1602,7 +1614,7 @@
           <t>10.0.2.15</t>
         </is>
       </c>
-      <c r="F33" s="1" t="n">
+      <c r="F33" s="2" t="n">
         <v>46142.55305555555</v>
       </c>
       <c r="G33" t="n">
@@ -1638,7 +1650,7 @@
           <t>10.0.2.15</t>
         </is>
       </c>
-      <c r="F34" s="1" t="n">
+      <c r="F34" s="2" t="n">
         <v>46142.55305555555</v>
       </c>
       <c r="G34" t="n">
@@ -1674,7 +1686,7 @@
           <t>10.0.2.15</t>
         </is>
       </c>
-      <c r="F35" s="1" t="n">
+      <c r="F35" s="2" t="n">
         <v>46142.55318287037</v>
       </c>
       <c r="G35" t="n">
@@ -1710,7 +1722,7 @@
           <t>10.0.2.15</t>
         </is>
       </c>
-      <c r="F36" s="1" t="n">
+      <c r="F36" s="2" t="n">
         <v>46142.55476851852</v>
       </c>
       <c r="G36" t="n">
@@ -1746,7 +1758,7 @@
           <t>10.0.2.15</t>
         </is>
       </c>
-      <c r="F37" s="1" t="n">
+      <c r="F37" s="2" t="n">
         <v>46142.55555555555</v>
       </c>
       <c r="G37" t="n">
@@ -1782,7 +1794,7 @@
           <t>192.168.53.159</t>
         </is>
       </c>
-      <c r="F38" s="1" t="n">
+      <c r="F38" s="2" t="n">
         <v>46143.53011574074</v>
       </c>
       <c r="G38" t="n">
@@ -1818,7 +1830,7 @@
           <t>192.168.53.159</t>
         </is>
       </c>
-      <c r="F39" s="1" t="n">
+      <c r="F39" s="2" t="n">
         <v>46143.53017361111</v>
       </c>
       <c r="G39" t="n">
@@ -1854,7 +1866,7 @@
           <t>192.168.53.159</t>
         </is>
       </c>
-      <c r="F40" s="1" t="n">
+      <c r="F40" s="2" t="n">
         <v>46143.53047453704</v>
       </c>
       <c r="G40" t="n">
@@ -1890,7 +1902,7 @@
           <t>192.168.53.159</t>
         </is>
       </c>
-      <c r="F41" s="1" t="n">
+      <c r="F41" s="2" t="n">
         <v>46143.53092592592</v>
       </c>
       <c r="G41" t="n">
@@ -1926,7 +1938,7 @@
           <t>192.168.53.159</t>
         </is>
       </c>
-      <c r="F42" s="1" t="n">
+      <c r="F42" s="2" t="n">
         <v>46143.53087962963</v>
       </c>
       <c r="G42" t="n">
@@ -1962,7 +1974,7 @@
           <t>192.168.53.159</t>
         </is>
       </c>
-      <c r="F43" s="1" t="n">
+      <c r="F43" s="2" t="n">
         <v>46143.53075231481</v>
       </c>
       <c r="G43" t="n">
@@ -1998,7 +2010,7 @@
           <t>192.168.156.159</t>
         </is>
       </c>
-      <c r="F44" s="1" t="n">
+      <c r="F44" s="2" t="n">
         <v>46143.96427083333</v>
       </c>
       <c r="G44" t="n">
@@ -2034,7 +2046,7 @@
           <t>192.168.29.124</t>
         </is>
       </c>
-      <c r="F45" s="1" t="n">
+      <c r="F45" s="2" t="n">
         <v>46144.94980324074</v>
       </c>
       <c r="G45" t="n">
@@ -2070,7 +2082,7 @@
           <t>192.168.29.124</t>
         </is>
       </c>
-      <c r="F46" s="1" t="n">
+      <c r="F46" s="2" t="n">
         <v>46144.94993055556</v>
       </c>
       <c r="G46" t="n">
@@ -2106,7 +2118,7 @@
           <t>192.168.29.124</t>
         </is>
       </c>
-      <c r="F47" s="1" t="n">
+      <c r="F47" s="2" t="n">
         <v>46144.9502199074</v>
       </c>
       <c r="G47" t="n">
@@ -2142,7 +2154,7 @@
           <t>192.168.29.124</t>
         </is>
       </c>
-      <c r="F48" s="1" t="n">
+      <c r="F48" s="2" t="n">
         <v>46144.95164351852</v>
       </c>
       <c r="G48" t="n">
@@ -2178,7 +2190,7 @@
           <t>192.168.29.124</t>
         </is>
       </c>
-      <c r="F49" s="1" t="n">
+      <c r="F49" s="2" t="n">
         <v>46144.95726851852</v>
       </c>
       <c r="G49" t="n">
@@ -2214,7 +2226,7 @@
           <t>192.168.29.124</t>
         </is>
       </c>
-      <c r="F50" s="1" t="n">
+      <c r="F50" s="2" t="n">
         <v>46144.95730324074</v>
       </c>
       <c r="G50" t="n">
@@ -2250,7 +2262,7 @@
           <t>192.168.29.124</t>
         </is>
       </c>
-      <c r="F51" s="1" t="n">
+      <c r="F51" s="2" t="n">
         <v>46144.9572337963</v>
       </c>
       <c r="G51" t="n">
@@ -2286,7 +2298,7 @@
           <t>192.168.29.124</t>
         </is>
       </c>
-      <c r="F52" s="1" t="n">
+      <c r="F52" s="2" t="n">
         <v>46144.95726851852</v>
       </c>
       <c r="G52" t="n">
@@ -2322,7 +2334,7 @@
           <t>192.168.29.124</t>
         </is>
       </c>
-      <c r="F53" s="1" t="n">
+      <c r="F53" s="2" t="n">
         <v>46144.95730324074</v>
       </c>
       <c r="G53" t="n">
@@ -2358,7 +2370,7 @@
           <t>192.168.29.124</t>
         </is>
       </c>
-      <c r="F54" s="1" t="n">
+      <c r="F54" s="2" t="n">
         <v>46144.95868055556</v>
       </c>
       <c r="G54" t="n">
@@ -2394,7 +2406,7 @@
           <t>192.168.29.124</t>
         </is>
       </c>
-      <c r="F55" s="1" t="n">
+      <c r="F55" s="2" t="n">
         <v>46144.95898148148</v>
       </c>
       <c r="G55" t="n">
@@ -2430,13 +2442,49 @@
           <t>192.168.29.124</t>
         </is>
       </c>
-      <c r="F56" s="1" t="n">
+      <c r="F56" s="2" t="n">
         <v>46144.95967592593</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
       </c>
       <c r="H56" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Session Hijacking</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>social enginnering</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>10.65.153.167</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>46145.55929398148</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="inlineStr">
         <is>
           <t>low</t>
         </is>

--- a/backend/Blockchain/leader/excel2.xlsx
+++ b/backend/Blockchain/leader/excel2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2562,6 +2562,42 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Cookie Stealing</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>data exfiltration</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>192.168.186.159</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>46146.71421296296</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/Blockchain/leader/excel2.xlsx
+++ b/backend/Blockchain/leader/excel2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2598,6 +2598,42 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>192.168.26.159</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Brute Force</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>authentication</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>192.168.26.159</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>46153.52240740741</v>
+      </c>
+      <c r="G61" t="n">
+        <v>11</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
